--- a/code/Created Files for Analysis/selected_indicators_final.xlsx
+++ b/code/Created Files for Analysis/selected_indicators_final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -634,22 +634,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WB-WDI-FM-AST-NFRG-CN</t>
+          <t>WB-WDI-EG-EGY-PRIM-PP-KD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Net foreign assets</t>
+          <t>Energy intensity level of primary energy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Net foreign assets are the sum of foreign assets held by monetary authorities and deposit money banks, less their foreign liabilities. Data are in current local currency.</t>
+          <t>Energy intensity level of primary energy is the ratio between energy supply and gross domestic product measured at purchasing power parity. Energy intensity is an indication of how much energy is used to produce one unit of economic output. Lower ratio indicates that less energy is used to produce one unit of output.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Netto-Auslandsvermögen monetärer Behörden: monetärer Bilanzindikator.</t>
+          <t>Energieintensität (MJ/$BIP): misst Energieeinsatz pro Einheit Wirtschaftsleistung.</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -659,28 +659,28 @@
         <v>100</v>
       </c>
       <c r="G8" t="n">
-        <v>94.59999999999999</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WB-WDI-EG-EGY-PRIM-PP-KD</t>
+          <t>WB-WDI-SL-UEM-TOTL-NE-ZS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Energy intensity level of primary energy</t>
+          <t>Unemployment, total (% of total labor force)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Energy intensity level of primary energy is the ratio between energy supply and gross domestic product measured at purchasing power parity. Energy intensity is an indication of how much energy is used to produce one unit of economic output. Lower ratio indicates that less energy is used to produce one unit of output.</t>
+          <t>Unemployment refers to the share of the labor force that is without work but available for and seeking employment. Definitions of labor force and unemployment differ by country.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Energieintensität (MJ/$BIP): misst Energieeinsatz pro Einheit Wirtschaftsleistung.</t>
+          <t>Arbeitslosenquote: einer der drei Kernindikatoren der Makroökonomie (Mankiw, 2013, S. 5).</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -690,28 +690,28 @@
         <v>100</v>
       </c>
       <c r="G9" t="n">
-        <v>90</v>
+        <v>79.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WB-WDI-SL-UEM-TOTL-NE-ZS</t>
+          <t>WB-WDI-SL-EMP-TOTL-SP-NE-ZS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Unemployment, total (% of total labor force)</t>
+          <t>Employment to population ratio, 15+, total (%)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Unemployment refers to the share of the labor force that is without work but available for and seeking employment. Definitions of labor force and unemployment differ by country.</t>
+          <t>Employment to population ratio is the proportion of a country's population that is employed. Employment is defined as persons of working age who, during a short reference period, were engaged in any activity to produce goods or provide services for pay or profit, whether at work during the reference period (i.e. who worked in a job for at least one hour) or not at work due to temporary absence from a job, or to working-time arrangements. Ages 15 and older are generally considered the working-age population.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Arbeitslosenquote: einer der drei Kernindikatoren der Makroökonomie (Mankiw, 2013, S. 5).</t>
+          <t>Gesamtbeschäftigungsquote: misst den Anteil der erwerbstätigen Bevölkerung.</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -721,59 +721,59 @@
         <v>100</v>
       </c>
       <c r="G10" t="n">
-        <v>79.3</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WB-WDI-SL-EMP-TOTL-SP-NE-ZS</t>
+          <t>WB-WDI-NY-GDP-PCAP-KD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Employment to population ratio, 15+, total (%)</t>
+          <t>GDP per capita</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Employment to population ratio is the proportion of a country's population that is employed. Employment is defined as persons of working age who, during a short reference period, were engaged in any activity to produce goods or provide services for pay or profit, whether at work during the reference period (i.e. who worked in a job for at least one hour) or not at work due to temporary absence from a job, or to working-time arrangements. Ages 15 and older are generally considered the working-age population.</t>
+          <t>GDP per capita is gross domestic product divided by midyear population. GDP is the sum of gross value added by all resident producers in the economy plus any product taxes and minus any subsidies not included in the value of the products. It is calculated without making deductions for depreciation of fabricated assets or for depletion and degradation of natural resources. Data are in constant 2015 U.S. dollars.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Gesamtbeschäftigungsquote: misst den Anteil der erwerbstätigen Bevölkerung.</t>
+          <t>BIP pro Kopf: meistgenutzter makroök. Wohlstandsindikator.</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F11" t="n">
-        <v>100</v>
+        <v>99.2</v>
       </c>
       <c r="G11" t="n">
-        <v>77.8</v>
+        <v>99.09999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WB-WDI-NY-GDP-PCAP-KD</t>
+          <t>WB-WDI-NY-GDP-MKTP-KD</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GDP per capita</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GDP per capita is gross domestic product divided by midyear population. GDP is the sum of gross value added by all resident producers in the economy plus any product taxes and minus any subsidies not included in the value of the products. It is calculated without making deductions for depreciation of fabricated assets or for depletion and degradation of natural resources. Data are in constant 2015 U.S. dollars.</t>
+          <t>GDP at purchaser's prices is the sum of gross value added by all resident producers in the economy plus any product taxes and minus any subsidies not included in the value of the products. It is calculated without making deductions for depreciation of fabricated assets or for depletion and degradation of natural resources. Data are in constant 2015 prices, expressed in U.S. dollars. Dollar figures for GDP are converted from domestic currencies using 2015 official exchange rates. For a few countries where the official exchange rate does not reflect the rate effectively applied to actual foreign exchange transactions, an alternative conversion factor is used.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>BIP pro Kopf: meistgenutzter makroök. Wohlstandsindikator.</t>
+          <t>Kernindikator der gesamtwirtschaftlichen Produktion (BIP).</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -783,28 +783,28 @@
         <v>99.2</v>
       </c>
       <c r="G12" t="n">
-        <v>99.09999999999999</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WB-WDI-NY-GDP-MKTP-KD</t>
+          <t>WB-WDI-TM-VAL-MMTL-ZS-UN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GDP</t>
+          <t>Ores and metals imports</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GDP at purchaser's prices is the sum of gross value added by all resident producers in the economy plus any product taxes and minus any subsidies not included in the value of the products. It is calculated without making deductions for depreciation of fabricated assets or for depletion and degradation of natural resources. Data are in constant 2015 prices, expressed in U.S. dollars. Dollar figures for GDP are converted from domestic currencies using 2015 official exchange rates. For a few countries where the official exchange rate does not reflect the rate effectively applied to actual foreign exchange transactions, an alternative conversion factor is used.</t>
+          <t>Ores and metals comprise commodities in SITC sections 27 (crude fertilizer, minerals nes); 28 (metalliferous ores, scrap); and 68 (non-ferrous metals).</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Kernindikator der gesamtwirtschaftlichen Produktion (BIP).</t>
+          <t>Rohstoffimporte Erze/Metalle (% Warenimporte): Außenhandelsstrukturindikator.</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -814,28 +814,28 @@
         <v>99.2</v>
       </c>
       <c r="G13" t="n">
-        <v>98.8</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WB-WDI-TM-VAL-MMTL-ZS-UN</t>
+          <t>WB-WDI-TM-VAL-AGRI-ZS-UN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ores and metals imports</t>
+          <t>Agricultural raw materials imports</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ores and metals comprise commodities in SITC sections 27 (crude fertilizer, minerals nes); 28 (metalliferous ores, scrap); and 68 (non-ferrous metals).</t>
+          <t>Agricultural raw materials comprise SITC section 2 (crude materials except fuels) excluding divisions 22, 27 (crude fertilizers and minerals excluding coal, petroleum, and precious stones), and 28 (metalliferous ores and scrap).</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Rohstoffimporte Erze/Metalle (% Warenimporte): Außenhandelsstrukturindikator.</t>
+          <t>Rohstoffimporte Agrar (% Warenimporte): Außenhandelsstrukturindikator.</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -845,28 +845,28 @@
         <v>99.2</v>
       </c>
       <c r="G14" t="n">
-        <v>92.09999999999999</v>
+        <v>91.90000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WB-WDI-TM-VAL-AGRI-ZS-UN</t>
+          <t>WB-WDI-SL-EMP-TOTL-SP-FE-NE-ZS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Agricultural raw materials imports</t>
+          <t>Employment to population ratio, 15+, female (%)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Agricultural raw materials comprise SITC section 2 (crude materials except fuels) excluding divisions 22, 27 (crude fertilizers and minerals excluding coal, petroleum, and precious stones), and 28 (metalliferous ores and scrap).</t>
+          <t>Employment to population ratio is the proportion of a country's population that is employed. Employment is defined as persons of working age who, during a short reference period, were engaged in any activity to produce goods or provide services for pay or profit, whether at work during the reference period (i.e. who worked in a job for at least one hour) or not at work due to temporary absence from a job, or to working-time arrangements. Ages 15 and older are generally considered the working-age population.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Rohstoffimporte Agrar (% Warenimporte): Außenhandelsstrukturindikator.</t>
+          <t>Beschäftigungsquote (Frauen): geschlechtsspezifischer Arbeitsmarktindikator.</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -876,59 +876,59 @@
         <v>99.2</v>
       </c>
       <c r="G15" t="n">
-        <v>91.90000000000001</v>
+        <v>75.40000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>WB-WDI-SL-EMP-TOTL-SP-FE-NE-ZS</t>
+          <t>WB-WDI-SL-GDP-PCAP-EM-KD</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Employment to population ratio, 15+, female (%)</t>
+          <t>GDP per person employed</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Employment to population ratio is the proportion of a country's population that is employed. Employment is defined as persons of working age who, during a short reference period, were engaged in any activity to produce goods or provide services for pay or profit, whether at work during the reference period (i.e. who worked in a job for at least one hour) or not at work due to temporary absence from a job, or to working-time arrangements. Ages 15 and older are generally considered the working-age population.</t>
+          <t>GDP per person employed is gross domestic product (GDP) divided by total employment in the economy. Purchasing power parity (PPP) GDP is GDP converted to 2017 constant international dollars using PPP rates. An international dollar has the same purchasing power over GDP that a U.S. dollar has in the United States.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Beschäftigungsquote (Frauen): geschlechtsspezifischer Arbeitsmarktindikator.</t>
+          <t>BIP pro Beschäftigten: gesamtwirtschaftliche Arbeitsproduktivität.</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F16" t="n">
-        <v>99.2</v>
+        <v>98.3</v>
       </c>
       <c r="G16" t="n">
-        <v>75.40000000000001</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>WB-WDI-SL-GDP-PCAP-EM-KD</t>
+          <t>WB-WDI-NE-CON-GOVT-CD</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GDP per person employed</t>
+          <t>General government final consumption expenditure</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GDP per person employed is gross domestic product (GDP) divided by total employment in the economy. Purchasing power parity (PPP) GDP is GDP converted to 2017 constant international dollars using PPP rates. An international dollar has the same purchasing power over GDP that a U.S. dollar has in the United States.</t>
+          <t>General government final consumption expenditure (formerly general government consumption) includes all government current expenditures for purchases of goods and services (including compensation of employees). It also includes most expenditures on national defense and security, but excludes government military expenditures that are part of government capital formation. Data are in current U.S. dollars.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>BIP pro Beschäftigten: gesamtwirtschaftliche Arbeitsproduktivität.</t>
+          <t>Staatlicher Endverbrauch: fiskalische Konsumkomponente des BIP.</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -938,28 +938,28 @@
         <v>98.3</v>
       </c>
       <c r="G17" t="n">
-        <v>98.2</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>WB-WDI-NE-CON-GOVT-CD</t>
+          <t>WB-WDI-SL-EMP-1524-SP-NE-ZS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>General government final consumption expenditure</t>
+          <t>Employment to population ratio, ages 15-24, total (%)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>General government final consumption expenditure (formerly general government consumption) includes all government current expenditures for purchases of goods and services (including compensation of employees). It also includes most expenditures on national defense and security, but excludes government military expenditures that are part of government capital formation. Data are in current U.S. dollars.</t>
+          <t>Employment to population ratio is the proportion of a country's population that is employed. Employment is defined as persons of working age who, during a short reference period, were engaged in any activity to produce goods or provide services for pay or profit, whether at work during the reference period (i.e. who worked in a job for at least one hour) or not at work due to temporary absence from a job, or to working-time arrangements. Ages 15-24 are generally considered the youth population.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Staatlicher Endverbrauch: fiskalische Konsumkomponente des BIP.</t>
+          <t>Beschäftigungsquote (15–24): Jugendarbeitsmarktindikator.</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -969,59 +969,59 @@
         <v>98.3</v>
       </c>
       <c r="G18" t="n">
-        <v>95.3</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>WB-WDI-SL-EMP-1524-SP-NE-ZS</t>
+          <t>WB-WDI-NY-ADJ-DRES-GN-ZS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Employment to population ratio, ages 15-24, total (%)</t>
+          <t>Adjusted savings: natural resources depletion</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Employment to population ratio is the proportion of a country's population that is employed. Employment is defined as persons of working age who, during a short reference period, were engaged in any activity to produce goods or provide services for pay or profit, whether at work during the reference period (i.e. who worked in a job for at least one hour) or not at work due to temporary absence from a job, or to working-time arrangements. Ages 15-24 are generally considered the youth population.</t>
+          <t>Natural resource depletion is the sum of net forest depletion, energy depletion, and mineral depletion. Net forest depletion is unit resource rents times the excess of roundwood harvest over natural growth. Energy depletion is the ratio of the value of the stock of energy resources to the remaining reserve lifetime (capped at 25 years). It covers coal, crude oil, and natural gas. Mineral depletion is the ratio of the value of the stock of mineral resources to the remaining reserve lifetime (capped at 25 years). It covers tin, gold, lead, zinc, iron, copper, nickel, silver, bauxite, and phosphate.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Beschäftigungsquote (15–24): Jugendarbeitsmarktindikator.</t>
+          <t>Ressourcenraubbewertung (% BNE): Teil der volkswirtschaftlichen Nachhaltigkeitsbuchführung (Adjusted Net Savings).</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F19" t="n">
-        <v>98.3</v>
+        <v>97.5</v>
       </c>
       <c r="G19" t="n">
-        <v>72.2</v>
+        <v>90.40000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>WB-WDI-NY-ADJ-DRES-GN-ZS</t>
+          <t>WB-WDI-TX-VAL-TECH-CD</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Adjusted savings: natural resources depletion</t>
+          <t>High-technology exports</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Natural resource depletion is the sum of net forest depletion, energy depletion, and mineral depletion. Net forest depletion is unit resource rents times the excess of roundwood harvest over natural growth. Energy depletion is the ratio of the value of the stock of energy resources to the remaining reserve lifetime (capped at 25 years). It covers coal, crude oil, and natural gas. Mineral depletion is the ratio of the value of the stock of mineral resources to the remaining reserve lifetime (capped at 25 years). It covers tin, gold, lead, zinc, iron, copper, nickel, silver, bauxite, and phosphate.</t>
+          <t>High-technology exports are products with high R&amp;D intensity, such as aerospace, computers, pharmaceuticals, scientific Instruments, and electrical machinery. Data are in current U.S. dollars.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Ressourcenraubbewertung (% BNE): Teil der volkswirtschaftlichen Nachhaltigkeitsbuchführung (Adjusted Net Savings).</t>
+          <t>Hochtechnologieexporte: misst Exportstruktur und Innovationsintensität.</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1031,59 +1031,59 @@
         <v>97.5</v>
       </c>
       <c r="G20" t="n">
-        <v>90.40000000000001</v>
+        <v>85.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>WB-WDI-TX-VAL-TECH-CD</t>
+          <t>WB-WDI-BM-KLT-DINV-WD-GD-ZS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>High-technology exports</t>
+          <t>Foreign direct investment, net outflows</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>High-technology exports are products with high R&amp;D intensity, such as aerospace, computers, pharmaceuticals, scientific Instruments, and electrical machinery. Data are in current U.S. dollars.</t>
+          <t>Foreign direct investment refers to direct investment equity flows in an economy. It is the sum of equity capital, reinvestment of earnings, and other capital. Direct investment is a category of cross-border investment associated with a resident in one economy having control or a significant degree of influence on the management of an enterprise that is resident in another economy. Ownership of 10 percent or more of the ordinary shares of voting stock is the criterion for determining the existence of a direct investment relationship. This series shows net outflows of investment from the reporting economy to the rest of the world, and is divided by GDP.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Hochtechnologieexporte: misst Exportstruktur und Innovationsintensität.</t>
+          <t>Netto-Direktinvestitionen (% BIP): makroök. Kapitalflussindikator.</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F21" t="n">
-        <v>97.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>85.8</v>
+        <v>94.09999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>WB-WDI-BM-KLT-DINV-WD-GD-ZS</t>
+          <t>WB-WDI-NE-EXP-GNFS-KD</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Foreign direct investment, net outflows</t>
+          <t>Exports of goods and services</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Foreign direct investment refers to direct investment equity flows in an economy. It is the sum of equity capital, reinvestment of earnings, and other capital. Direct investment is a category of cross-border investment associated with a resident in one economy having control or a significant degree of influence on the management of an enterprise that is resident in another economy. Ownership of 10 percent or more of the ordinary shares of voting stock is the criterion for determining the existence of a direct investment relationship. This series shows net outflows of investment from the reporting economy to the rest of the world, and is divided by GDP.</t>
+          <t>Exports of goods and services represent the value of all goods and other market services provided to the rest of the world. They include the value of merchandise, freight, Insurance, transport, travel, royalties, license fees, and other services, such as communication, construction, financial, information, business, personal, and government services. They exclude compensation of employees and investment income (formerly called factor services) and transfer payments. Data are in constant 2015 prices, expressed in U.S. dollars.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Netto-Direktinvestitionen (% BIP): makroök. Kapitalflussindikator.</t>
+          <t>Exporte von Gütern und Dienstleistungen: Außenhandelskomponente der VGR.</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1093,59 +1093,59 @@
         <v>96.59999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>94.09999999999999</v>
+        <v>90.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>WB-WDI-NE-EXP-GNFS-KD</t>
+          <t>WB-WDI-NE-GDI-TOTL-KD</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Exports of goods and services</t>
+          <t>Gross capital formation</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Exports of goods and services represent the value of all goods and other market services provided to the rest of the world. They include the value of merchandise, freight, Insurance, transport, travel, royalties, license fees, and other services, such as communication, construction, financial, information, business, personal, and government services. They exclude compensation of employees and investment income (formerly called factor services) and transfer payments. Data are in constant 2015 prices, expressed in U.S. dollars.</t>
+          <t>Gross capital formation (formerly gross domestic investment) consists of outlays on additions to the fixed assets of the economy plus net changes in the level of inventories. Fixed assets include land improvements (fences, ditches, draIns, and so on); plant, machinery, and equipment purchases; and the construction of roads, railways, and the like, including schools, offices, hospitals, private residential dwellings, and commercial and industrial buildings. Inventories are stocks of goods held by firms to meet temporary or unexpected fluctuations in production or sales, and "work in progress." According to the 2008 SNA, net acquisitions of valuables are also considered capital formation. Data are in constant 2015 prices, expressed in U.S. dollars.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Exporte von Gütern und Dienstleistungen: Außenhandelskomponente der VGR.</t>
+          <t>Bruttoanlageinvestitionen: Investitionskomponente des BIP (VGR).</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F23" t="n">
-        <v>96.59999999999999</v>
+        <v>95.8</v>
       </c>
       <c r="G23" t="n">
-        <v>90.7</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>WB-WDI-NE-GDI-TOTL-KD</t>
+          <t>WB-WDI-SE-XPD-TOTL-GD-ZS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Gross capital formation</t>
+          <t>Government expenditure on education, total</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Gross capital formation (formerly gross domestic investment) consists of outlays on additions to the fixed assets of the economy plus net changes in the level of inventories. Fixed assets include land improvements (fences, ditches, draIns, and so on); plant, machinery, and equipment purchases; and the construction of roads, railways, and the like, including schools, offices, hospitals, private residential dwellings, and commercial and industrial buildings. Inventories are stocks of goods held by firms to meet temporary or unexpected fluctuations in production or sales, and "work in progress." According to the 2008 SNA, net acquisitions of valuables are also considered capital formation. Data are in constant 2015 prices, expressed in U.S. dollars.</t>
+          <t>General government expenditure on education (current, capital, and transfers) is expressed as a percentage of GDP. It includes expenditure funded by transfers from international sources to government. General government usually refers to local, regional and central governments.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Bruttoanlageinvestitionen: Investitionskomponente des BIP (VGR).</t>
+          <t>Staatliche Bildungsausgaben (% BIP): fiskalpolitischer Ausgabenindikator.</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1155,59 +1155,59 @@
         <v>95.8</v>
       </c>
       <c r="G24" t="n">
-        <v>86</v>
+        <v>80.90000000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>WB-WDI-SE-XPD-TOTL-GD-ZS</t>
+          <t>WB-CWON-NFA-PC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Government expenditure on education, total</t>
+          <t>Net foreign assets per capita</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>General government expenditure on education (current, capital, and transfers) is expressed as a percentage of GDP. It includes expenditure funded by transfers from international sources to government. General government usually refers to local, regional and central governments.</t>
+          <t>Foreign assets minus foreign liabilities</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Staatliche Bildungsausgaben (% BIP): fiskalpolitischer Ausgabenindikator.</t>
+          <t>Netto-Auslandsvermögen pro Kopf: ökonomische Außenbilanzgröße.</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F25" t="n">
-        <v>95.8</v>
+        <v>93.3</v>
       </c>
       <c r="G25" t="n">
-        <v>80.90000000000001</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>WB-CWON-NFA-PC</t>
+          <t>WB-CWON-PCA-PC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Net foreign assets per capita</t>
+          <t>Produced capital per capita</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Foreign assets minus foreign liabilities</t>
+          <t>Value of machinery, buildings, equipment, and residential and nonresidential urban land</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Netto-Auslandsvermögen pro Kopf: ökonomische Außenbilanzgröße.</t>
+          <t>Physischer Kapitalstock pro Kopf (Maschinen, Gebäude): ökonomische Vermögensgröße.</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1217,37 +1217,6 @@
         <v>93.3</v>
       </c>
       <c r="G26" t="n">
-        <v>69.90000000000001</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>WB-CWON-PCA-PC</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Produced capital per capita</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Value of machinery, buildings, equipment, and residential and nonresidential urban land</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Physischer Kapitalstock pro Kopf (Maschinen, Gebäude): ökonomische Vermögensgröße.</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>111</v>
-      </c>
-      <c r="F27" t="n">
-        <v>93.3</v>
-      </c>
-      <c r="G27" t="n">
         <v>69.90000000000001</v>
       </c>
     </row>
